--- a/BASE_ONBOARDING_ESCUELA_COMERCIAL (4).xlsx
+++ b/BASE_ONBOARDING_ESCUELA_COMERCIAL (4).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cuneduco-my.sharepoint.com/personal/yeison_oyolat_cun_edu_co/Documents/Documentos/Margaret/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="557" documentId="8_{9A6E4651-CE0E-4C4F-9362-9772CBD3C2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E650A2A-70B9-47EB-B3E1-32AD72F9AB15}"/>
+  <xr:revisionPtr revIDLastSave="559" documentId="8_{9A6E4651-CE0E-4C4F-9362-9772CBD3C2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F0355D0-096A-4623-AF39-6E0AF68F8850}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17181,6 +17181,136 @@
     </row>
   </sheetData>
   <mergeCells count="150">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="D2:D6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="E17:E21"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="C22:C26"/>
+    <mergeCell ref="D22:D26"/>
+    <mergeCell ref="E22:E26"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="C27:C31"/>
+    <mergeCell ref="D27:D31"/>
+    <mergeCell ref="E27:E31"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="D32:D36"/>
+    <mergeCell ref="E32:E36"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="D37:D41"/>
+    <mergeCell ref="E37:E41"/>
+    <mergeCell ref="A42:A46"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="C42:C46"/>
+    <mergeCell ref="D42:D46"/>
+    <mergeCell ref="E42:E46"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="D47:D51"/>
+    <mergeCell ref="E47:E51"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="B52:B56"/>
+    <mergeCell ref="C52:C56"/>
+    <mergeCell ref="D52:D56"/>
+    <mergeCell ref="E52:E56"/>
+    <mergeCell ref="A57:A61"/>
+    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="C57:C61"/>
+    <mergeCell ref="D57:D61"/>
+    <mergeCell ref="E57:E61"/>
+    <mergeCell ref="A62:A66"/>
+    <mergeCell ref="B62:B66"/>
+    <mergeCell ref="C62:C66"/>
+    <mergeCell ref="D62:D66"/>
+    <mergeCell ref="E62:E66"/>
+    <mergeCell ref="A67:A71"/>
+    <mergeCell ref="B67:B71"/>
+    <mergeCell ref="C67:C71"/>
+    <mergeCell ref="D67:D71"/>
+    <mergeCell ref="E67:E71"/>
+    <mergeCell ref="A72:A76"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="C72:C76"/>
+    <mergeCell ref="D72:D76"/>
+    <mergeCell ref="E72:E76"/>
+    <mergeCell ref="A77:A81"/>
+    <mergeCell ref="B77:B81"/>
+    <mergeCell ref="C77:C81"/>
+    <mergeCell ref="D77:D81"/>
+    <mergeCell ref="E77:E81"/>
+    <mergeCell ref="A82:A86"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="C82:C86"/>
+    <mergeCell ref="D82:D86"/>
+    <mergeCell ref="E82:E86"/>
+    <mergeCell ref="A87:A91"/>
+    <mergeCell ref="B87:B91"/>
+    <mergeCell ref="C87:C91"/>
+    <mergeCell ref="D87:D91"/>
+    <mergeCell ref="E87:E91"/>
+    <mergeCell ref="A92:A96"/>
+    <mergeCell ref="B92:B96"/>
+    <mergeCell ref="C92:C96"/>
+    <mergeCell ref="D92:D96"/>
+    <mergeCell ref="E92:E96"/>
+    <mergeCell ref="A97:A101"/>
+    <mergeCell ref="B97:B101"/>
+    <mergeCell ref="C97:C101"/>
+    <mergeCell ref="D97:D101"/>
+    <mergeCell ref="E97:E101"/>
+    <mergeCell ref="A102:A106"/>
+    <mergeCell ref="B102:B106"/>
+    <mergeCell ref="C102:C106"/>
+    <mergeCell ref="D102:D106"/>
+    <mergeCell ref="E102:E106"/>
+    <mergeCell ref="A107:A111"/>
+    <mergeCell ref="B107:B111"/>
+    <mergeCell ref="C107:C111"/>
+    <mergeCell ref="D107:D111"/>
+    <mergeCell ref="E107:E111"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="C112:C116"/>
+    <mergeCell ref="D112:D116"/>
+    <mergeCell ref="E112:E116"/>
+    <mergeCell ref="A117:A121"/>
+    <mergeCell ref="B117:B121"/>
+    <mergeCell ref="C117:C121"/>
+    <mergeCell ref="D117:D121"/>
+    <mergeCell ref="E117:E121"/>
+    <mergeCell ref="A122:A126"/>
+    <mergeCell ref="B122:B126"/>
+    <mergeCell ref="C122:C126"/>
+    <mergeCell ref="D122:D126"/>
+    <mergeCell ref="E122:E126"/>
+    <mergeCell ref="A127:A131"/>
+    <mergeCell ref="B127:B131"/>
+    <mergeCell ref="C127:C131"/>
+    <mergeCell ref="D127:D131"/>
+    <mergeCell ref="E127:E131"/>
     <mergeCell ref="A132:A136"/>
     <mergeCell ref="B132:B136"/>
     <mergeCell ref="C132:C136"/>
@@ -17201,136 +17331,6 @@
     <mergeCell ref="C142:C146"/>
     <mergeCell ref="D142:D146"/>
     <mergeCell ref="E142:E146"/>
-    <mergeCell ref="A122:A126"/>
-    <mergeCell ref="B122:B126"/>
-    <mergeCell ref="C122:C126"/>
-    <mergeCell ref="D122:D126"/>
-    <mergeCell ref="E122:E126"/>
-    <mergeCell ref="A127:A131"/>
-    <mergeCell ref="B127:B131"/>
-    <mergeCell ref="C127:C131"/>
-    <mergeCell ref="D127:D131"/>
-    <mergeCell ref="E127:E131"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="C112:C116"/>
-    <mergeCell ref="D112:D116"/>
-    <mergeCell ref="E112:E116"/>
-    <mergeCell ref="A117:A121"/>
-    <mergeCell ref="B117:B121"/>
-    <mergeCell ref="C117:C121"/>
-    <mergeCell ref="D117:D121"/>
-    <mergeCell ref="E117:E121"/>
-    <mergeCell ref="A102:A106"/>
-    <mergeCell ref="B102:B106"/>
-    <mergeCell ref="C102:C106"/>
-    <mergeCell ref="D102:D106"/>
-    <mergeCell ref="E102:E106"/>
-    <mergeCell ref="A107:A111"/>
-    <mergeCell ref="B107:B111"/>
-    <mergeCell ref="C107:C111"/>
-    <mergeCell ref="D107:D111"/>
-    <mergeCell ref="E107:E111"/>
-    <mergeCell ref="A92:A96"/>
-    <mergeCell ref="B92:B96"/>
-    <mergeCell ref="C92:C96"/>
-    <mergeCell ref="D92:D96"/>
-    <mergeCell ref="E92:E96"/>
-    <mergeCell ref="A97:A101"/>
-    <mergeCell ref="B97:B101"/>
-    <mergeCell ref="C97:C101"/>
-    <mergeCell ref="D97:D101"/>
-    <mergeCell ref="E97:E101"/>
-    <mergeCell ref="A82:A86"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="C82:C86"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="E82:E86"/>
-    <mergeCell ref="A87:A91"/>
-    <mergeCell ref="B87:B91"/>
-    <mergeCell ref="C87:C91"/>
-    <mergeCell ref="D87:D91"/>
-    <mergeCell ref="E87:E91"/>
-    <mergeCell ref="A72:A76"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="C72:C76"/>
-    <mergeCell ref="D72:D76"/>
-    <mergeCell ref="E72:E76"/>
-    <mergeCell ref="A77:A81"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="C77:C81"/>
-    <mergeCell ref="D77:D81"/>
-    <mergeCell ref="E77:E81"/>
-    <mergeCell ref="A62:A66"/>
-    <mergeCell ref="B62:B66"/>
-    <mergeCell ref="C62:C66"/>
-    <mergeCell ref="D62:D66"/>
-    <mergeCell ref="E62:E66"/>
-    <mergeCell ref="A67:A71"/>
-    <mergeCell ref="B67:B71"/>
-    <mergeCell ref="C67:C71"/>
-    <mergeCell ref="D67:D71"/>
-    <mergeCell ref="E67:E71"/>
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="B52:B56"/>
-    <mergeCell ref="C52:C56"/>
-    <mergeCell ref="D52:D56"/>
-    <mergeCell ref="E52:E56"/>
-    <mergeCell ref="A57:A61"/>
-    <mergeCell ref="B57:B61"/>
-    <mergeCell ref="C57:C61"/>
-    <mergeCell ref="D57:D61"/>
-    <mergeCell ref="E57:E61"/>
-    <mergeCell ref="A42:A46"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="C42:C46"/>
-    <mergeCell ref="D42:D46"/>
-    <mergeCell ref="E42:E46"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="C47:C51"/>
-    <mergeCell ref="D47:D51"/>
-    <mergeCell ref="E47:E51"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="C32:C36"/>
-    <mergeCell ref="D32:D36"/>
-    <mergeCell ref="E32:E36"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="D37:D41"/>
-    <mergeCell ref="E37:E41"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="C22:C26"/>
-    <mergeCell ref="D22:D26"/>
-    <mergeCell ref="E22:E26"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="C27:C31"/>
-    <mergeCell ref="D27:D31"/>
-    <mergeCell ref="E27:E31"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="E17:E21"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="D2:D6"/>
-    <mergeCell ref="E2:E6"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="E7:E11"/>
   </mergeCells>
   <conditionalFormatting sqref="I2:I151">
     <cfRule type="dataBar" priority="3">
